--- a/data/raw/김포 25년/항공통계상세조회(노선) (1).xlsx
+++ b/data/raw/김포 25년/항공통계상세조회(노선) (1).xlsx
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>10243</t>
-  </si>
-  <si>
-    <t>1749954</t>
-  </si>
-  <si>
-    <t>15482</t>
+    <t>5119</t>
+  </si>
+  <si>
+    <t>882814</t>
+  </si>
+  <si>
+    <t>7247</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,166 +53,166 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>35800</t>
+  </si>
+  <si>
+    <t>458</t>
+  </si>
+  <si>
+    <t>광주(KWJ)</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>6208</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>733</t>
+  </si>
+  <si>
+    <t>111559</t>
+  </si>
+  <si>
+    <t>434</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>5055</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
     <t>372</t>
   </si>
   <si>
-    <t>70106</t>
-  </si>
-  <si>
-    <t>888</t>
-  </si>
-  <si>
-    <t>광주(KWJ)</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>12225</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1445</t>
-  </si>
-  <si>
-    <t>219514</t>
-  </si>
-  <si>
-    <t>876</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
+    <t>83569</t>
+  </si>
+  <si>
+    <t>1717</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>9641</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>6466</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
   </si>
   <si>
     <t>62</t>
   </si>
   <si>
-    <t>10350</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>744</t>
-  </si>
-  <si>
-    <t>156423</t>
-  </si>
-  <si>
-    <t>2641</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>20859</t>
-  </si>
-  <si>
-    <t>268</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>13161</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
+    <t>10321</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>8940</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>10534</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3160</t>
+  </si>
+  <si>
+    <t>563176</t>
+  </si>
+  <si>
+    <t>3776</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>6401</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>1788</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
   </si>
   <si>
     <t>124</t>
   </si>
   <si>
-    <t>20914</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>17772</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>20972</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>6345</t>
-  </si>
-  <si>
-    <t>1122566</t>
-  </si>
-  <si>
-    <t>9070</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>13484</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>3632</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>47976</t>
-  </si>
-  <si>
-    <t>911</t>
+    <t>23356</t>
+  </si>
+  <si>
+    <t>300</t>
   </si>
 </sst>
 </file>
